--- a/DKS.xlsx
+++ b/DKS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2B5010-0340-41BD-9129-9358C8543CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF76DCF-26B5-4956-9966-EE0B9D734F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{AEDF7C68-C22C-401E-A9BD-35ACF1F87F21}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{AEDF7C68-C22C-401E-A9BD-35ACF1F87F21}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={89F3C0FF-08AB-4D72-A95D-E11A79CC87F0}</author>
+  </authors>
+  <commentList>
+    <comment ref="T17" authorId="0" shapeId="0" xr:uid="{89F3C0FF-08AB-4D72-A95D-E11A79CC87F0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    164,191 Merger &amp; integration cost</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Dicks Sporting Goods</t>
   </si>
@@ -166,6 +184,30 @@
   </si>
   <si>
     <t>2.4 billion USD -&gt; 24$ per Share</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>Foot Locker Stores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DICK'S </t>
+  </si>
+  <si>
+    <t>Foot Locker</t>
   </si>
 </sst>
 </file>
@@ -175,13 +217,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -211,6 +259,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -231,19 +285,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -260,6 +319,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{F1AFA14E-AAA8-4A10-8D0A-82682E2D6BA7}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,6 +642,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="T17" dT="2026-05-17T10:55:01.96" personId="{F1AFA14E-AAA8-4A10-8D0A-82682E2D6BA7}" id="{89F3C0FF-08AB-4D72-A95D-E11A79CC87F0}">
+    <text>164,191 Merger &amp; integration cost</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C17DCF2-F4E9-43E1-BAD1-D2BD4F389259}">
   <dimension ref="A1:K16"/>
@@ -599,7 +672,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>180.8</v>
+        <v>215.35</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -607,11 +680,11 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <f>56.285053+23.570633</f>
-        <v>79.855685999999992</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>12</v>
+        <f>65.474242+23.570633</f>
+        <v>89.044875000000005</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -620,7 +693,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>14437.908028799999</v>
+        <v>19175.813831250001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -628,10 +701,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>1689.94</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>12</v>
+        <v>1353.2260000000001</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -639,11 +712,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <f>0+1484.217</f>
-        <v>1484.2170000000001</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>12</v>
+        <v>1905.299</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -652,7 +724,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>14232.185028799999</v>
+        <v>19727.886831250002</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -677,8 +749,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A52A1C-0059-44B5-8437-E4B9478204D5}">
-  <dimension ref="A1:AM24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A52A1C-0059-44B5-8437-E4B9478204D5}">
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -686,12 +758,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
@@ -716,43 +788,64 @@
       <c r="J2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="T2" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="2">
+      <c r="R3" s="2">
         <v>722</v>
       </c>
-      <c r="O3" s="2">
+      <c r="S3" s="2">
         <v>723</v>
       </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="T3" s="2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="2">
+      <c r="R4" s="2">
         <v>131</v>
       </c>
-      <c r="O4" s="2">
+      <c r="S4" s="2">
         <v>133</v>
       </c>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="T4" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
@@ -766,67 +859,87 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1">
-        <f t="shared" ref="M5" si="0">+M3+M4</f>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
+        <f t="shared" ref="Q5" si="0">+Q3+Q4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="1">
-        <f>+N3+N4</f>
+      <c r="R5" s="1">
+        <f>+R3+R4</f>
         <v>853</v>
       </c>
-      <c r="O5" s="1">
-        <f>+O3+O4</f>
+      <c r="S5" s="1">
+        <f>+S3+S4</f>
         <v>856</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3">
-        <v>4952.2</v>
-      </c>
-      <c r="N7" s="3">
-        <v>4915.5</v>
-      </c>
-      <c r="O7" s="3">
-        <v>4899.3</v>
-      </c>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>38</v>
+      <c r="T5" s="1">
+        <f>+T3+T4</f>
+        <v>888</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="9">
+        <v>2593</v>
+      </c>
+      <c r="T6" s="9">
+        <v>2561</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -838,20 +951,22 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3">
-        <v>4218.1000000000004</v>
-      </c>
-      <c r="N8" s="3">
-        <v>4329.8</v>
-      </c>
-      <c r="O8" s="3">
-        <v>4425.3999999999996</v>
-      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
-        <v>39</v>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3">
+        <v>13442.849</v>
+      </c>
+      <c r="T8" s="3">
+        <v>14108.942999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -863,20 +978,22 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3">
-        <v>2979.1</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3388.7</v>
-      </c>
-      <c r="O9" s="3">
-        <v>3829</v>
-      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="10">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>3106.1770000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -888,44 +1005,101 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3">
-        <v>218.8</v>
-      </c>
-      <c r="N10" s="3">
-        <v>350.4</v>
-      </c>
-      <c r="O10" s="3">
-        <v>289.10000000000002</v>
-      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6">
-        <v>12368.198</v>
-      </c>
-      <c r="N11" s="6">
-        <v>12984.398999999999</v>
-      </c>
-      <c r="O11" s="6">
-        <v>13442.849</v>
-      </c>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3">
+        <v>4952.2</v>
+      </c>
+      <c r="R10" s="3">
+        <v>4915.5</v>
+      </c>
+      <c r="S10" s="3">
+        <v>4899.3</v>
+      </c>
+      <c r="T10" s="3">
+        <v>6888</v>
+      </c>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3">
+        <v>4218.1000000000004</v>
+      </c>
+      <c r="R11" s="3">
+        <v>4329.8</v>
+      </c>
+      <c r="S11" s="3">
+        <v>4425.3999999999996</v>
+      </c>
+      <c r="T11" s="3">
+        <v>5048.3</v>
+      </c>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -937,20 +1111,22 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="3">
-        <v>8083.64</v>
-      </c>
-      <c r="N12" s="3">
-        <v>8450.6640000000007</v>
-      </c>
-      <c r="O12" s="3">
-        <v>8617.1530000000002</v>
-      </c>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="Q12" s="3">
+        <v>2979.1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3388.7</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3829</v>
+      </c>
+      <c r="T12" s="3">
+        <v>4895.3999999999996</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -970,10 +1146,13 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -984,27 +1163,23 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <f t="shared" ref="L13" si="1">+L6-L11+L12</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <f t="shared" ref="M13:N13" si="2">+M11-M12</f>
-        <v>4284.558</v>
-      </c>
-      <c r="N13" s="3">
-        <f t="shared" si="2"/>
-        <v>4533.7349999999988</v>
-      </c>
-      <c r="O13" s="3">
-        <f>+O11-O12</f>
-        <v>4825.6959999999999</v>
-      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="Q13" s="3">
+        <v>218.8</v>
+      </c>
+      <c r="R13" s="3">
+        <v>350.4</v>
+      </c>
+      <c r="S13" s="3">
+        <v>289.10000000000002</v>
+      </c>
+      <c r="T13" s="3">
+        <v>383.4</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1024,58 +1199,66 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3">
-        <v>2799.8530000000001</v>
-      </c>
-      <c r="N14" s="3">
-        <v>3183.53</v>
-      </c>
-      <c r="O14" s="3">
-        <v>3294.2719999999999</v>
-      </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6">
+        <v>12368.198</v>
+      </c>
+      <c r="R14" s="6">
+        <v>12984.398999999999</v>
+      </c>
+      <c r="S14" s="6">
+        <v>13442.849</v>
+      </c>
+      <c r="T14" s="6">
+        <v>17215.12</v>
+      </c>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="6"/>
+      <c r="AO14" s="6"/>
+      <c r="AP14" s="6"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1087,20 +1270,22 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3">
-        <v>21.686</v>
-      </c>
-      <c r="N15" s="3">
-        <v>67.84</v>
-      </c>
-      <c r="O15" s="3">
-        <v>57.491999999999997</v>
-      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="Q15" s="3">
+        <v>8083.64</v>
+      </c>
+      <c r="R15" s="3">
+        <v>8450.6640000000007</v>
+      </c>
+      <c r="S15" s="3">
+        <v>8617.1530000000002</v>
+      </c>
+      <c r="T15" s="3">
+        <v>11547.858</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1120,10 +1305,14 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1134,27 +1323,30 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <f t="shared" ref="L16" si="3">+L13-L14+L15</f>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3">
+        <f t="shared" ref="P16" si="1">+P8-P14+P15</f>
         <v>0</v>
       </c>
-      <c r="M16" s="3">
-        <f t="shared" ref="M16:N16" si="4">+M13-M14-M15</f>
-        <v>1463.019</v>
-      </c>
-      <c r="N16" s="3">
-        <f t="shared" si="4"/>
-        <v>1282.3649999999986</v>
-      </c>
-      <c r="O16" s="3">
-        <f>+O13-O14-O15</f>
-        <v>1473.932</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="Q16" s="3">
+        <f t="shared" ref="Q16:R16" si="2">+Q14-Q15</f>
+        <v>4284.558</v>
+      </c>
+      <c r="R16" s="3">
+        <f t="shared" si="2"/>
+        <v>4533.7349999999988</v>
+      </c>
+      <c r="S16" s="3">
+        <f>+S14-S15</f>
+        <v>4825.6959999999999</v>
+      </c>
+      <c r="T16" s="3">
+        <f>+T14-T15</f>
+        <v>5667.2619999999988</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -1174,10 +1366,14 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
-    </row>
-    <row r="17" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1189,20 +1385,23 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="3">
-        <v>95.22</v>
-      </c>
-      <c r="N17" s="3">
-        <v>58.023000000000003</v>
-      </c>
-      <c r="O17" s="3">
-        <v>52.987000000000002</v>
-      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
+      <c r="Q17" s="3">
+        <v>2799.8530000000001</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3183.53</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3294.2719999999999</v>
+      </c>
+      <c r="T17" s="3">
+        <f>4338.162+164.191</f>
+        <v>4502.3530000000001</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -1222,10 +1421,14 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
-    </row>
-    <row r="18" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1237,20 +1440,22 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3">
-        <v>15.949</v>
-      </c>
-      <c r="N18" s="3">
-        <v>93.808999999999997</v>
-      </c>
-      <c r="O18" s="3">
-        <v>98.087999999999994</v>
-      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+      <c r="Q18" s="3">
+        <v>21.686</v>
+      </c>
+      <c r="R18" s="3">
+        <v>67.84</v>
+      </c>
+      <c r="S18" s="3">
+        <v>57.491999999999997</v>
+      </c>
+      <c r="T18" s="3">
+        <v>69</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -1270,10 +1475,14 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
-    </row>
-    <row r="19" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1284,27 +1493,30 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="3">
-        <f t="shared" ref="L19:N19" si="5">+L16-L17+L18</f>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3">
+        <f t="shared" ref="P19" si="3">+P16-P17+P18</f>
         <v>0</v>
       </c>
-      <c r="M19" s="3">
-        <f t="shared" si="5"/>
-        <v>1383.748</v>
-      </c>
-      <c r="N19" s="3">
-        <f t="shared" si="5"/>
-        <v>1318.1509999999987</v>
-      </c>
-      <c r="O19" s="3">
-        <f>+O16-O17+O18</f>
-        <v>1519.0329999999999</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="Q19" s="3">
+        <f t="shared" ref="Q19:R19" si="4">+Q16-Q17-Q18</f>
+        <v>1463.019</v>
+      </c>
+      <c r="R19" s="3">
+        <f t="shared" si="4"/>
+        <v>1282.3649999999986</v>
+      </c>
+      <c r="S19" s="3">
+        <f>+S16-S17-S18</f>
+        <v>1473.932</v>
+      </c>
+      <c r="T19" s="3">
+        <f>+T16-T17-T18</f>
+        <v>1095.9089999999987</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -1324,10 +1536,14 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
-    </row>
-    <row r="20" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1339,20 +1555,22 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3">
-        <v>340.61</v>
-      </c>
-      <c r="N20" s="3">
-        <v>271.63200000000001</v>
-      </c>
-      <c r="O20" s="3">
-        <v>353.72500000000002</v>
-      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="Q20" s="3">
+        <v>95.22</v>
+      </c>
+      <c r="R20" s="3">
+        <v>58.023000000000003</v>
+      </c>
+      <c r="S20" s="3">
+        <v>52.987000000000002</v>
+      </c>
+      <c r="T20" s="3">
+        <v>64.263000000000005</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -1372,10 +1590,14 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
-    </row>
-    <row r="21" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1386,27 +1608,23 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="3">
-        <f t="shared" ref="L21:N21" si="6">+L19-L20</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="6"/>
-        <v>1043.1379999999999</v>
-      </c>
-      <c r="N21" s="3">
-        <f t="shared" si="6"/>
-        <v>1046.5189999999986</v>
-      </c>
-      <c r="O21" s="3">
-        <f>+O19-O20</f>
-        <v>1165.308</v>
-      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="Q21" s="3">
+        <v>15.949</v>
+      </c>
+      <c r="R21" s="3">
+        <v>93.808999999999997</v>
+      </c>
+      <c r="S21" s="3">
+        <v>98.087999999999994</v>
+      </c>
+      <c r="T21" s="3">
+        <v>110.327</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -1426,8 +1644,15 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
-    </row>
-    <row r="22" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="3"/>
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="2:43" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1441,11 +1666,26 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+      <c r="P22" s="3">
+        <f t="shared" ref="P22:R22" si="5">+P19-P20+P21</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" si="5"/>
+        <v>1383.748</v>
+      </c>
+      <c r="R22" s="3">
+        <f t="shared" si="5"/>
+        <v>1318.1509999999987</v>
+      </c>
+      <c r="S22" s="3">
+        <f>+S19-S20+S21</f>
+        <v>1519.0329999999999</v>
+      </c>
+      <c r="T22" s="3">
+        <f>+T19-T20+T21</f>
+        <v>1141.9729999999988</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -1465,52 +1705,229 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
-    </row>
-    <row r="23" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3">
+        <v>340.61</v>
+      </c>
+      <c r="R23" s="3">
+        <v>271.63200000000001</v>
+      </c>
+      <c r="S23" s="3">
+        <v>353.72500000000002</v>
+      </c>
+      <c r="T23" s="3">
+        <v>292.73399999999998</v>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="2:43" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3">
+        <f t="shared" ref="P24:R24" si="6">+P22-P23</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="6"/>
+        <v>1043.1379999999999</v>
+      </c>
+      <c r="R24" s="3">
+        <f t="shared" si="6"/>
+        <v>1046.5189999999986</v>
+      </c>
+      <c r="S24" s="3">
+        <f>+S22-S23</f>
+        <v>1165.308</v>
+      </c>
+      <c r="T24" s="3">
+        <f>+T22-T23</f>
+        <v>849.2389999999989</v>
+      </c>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="3"/>
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="2:43" x14ac:dyDescent="0.2">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="2:43" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J23" s="7" t="e">
-        <f t="shared" ref="J23:N23" si="7">+J21/J24</f>
+      <c r="J26" s="7" t="e">
+        <f t="shared" ref="J26:R26" si="7">+J24/J27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7" t="e">
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M23" s="7">
+      <c r="Q26" s="7">
         <f t="shared" si="7"/>
         <v>13.430039138943249</v>
       </c>
-      <c r="N23" s="7">
+      <c r="R26" s="7">
         <f t="shared" si="7"/>
         <v>12.715596218803899</v>
       </c>
-      <c r="O23" s="7">
-        <f>+O21/O24</f>
+      <c r="S26" s="7">
+        <f>+S24/S27</f>
         <v>14.481632450166526</v>
       </c>
-    </row>
-    <row r="24" spans="2:39" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
+      <c r="T26" s="7">
+        <f>+T24/T27</f>
+        <v>10.215180128706308</v>
+      </c>
+    </row>
+    <row r="27" spans="2:43" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7">
         <v>77.671999999999997</v>
       </c>
-      <c r="N24" s="7">
+      <c r="R27" s="7">
         <v>82.302000000000007</v>
       </c>
-      <c r="O24" s="7">
+      <c r="S27" s="7">
         <v>80.468000000000004</v>
+      </c>
+      <c r="T27" s="2">
+        <v>83.135000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1518,5 +1935,6 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{35F0D976-AB52-4B9A-9CB3-401B736D99E7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/DKS.xlsx
+++ b/DKS.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF76DCF-26B5-4956-9966-EE0B9D734F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9151F33D-54B1-4158-887F-8C68D3EAD73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{AEDF7C68-C22C-401E-A9BD-35ACF1F87F21}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Dicks Sporting Goods</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Foot Locker</t>
+  </si>
+  <si>
+    <t>IR</t>
   </si>
 </sst>
 </file>
@@ -224,6 +227,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -259,12 +268,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -285,24 +288,28 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -672,28 +679,30 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>215.35</v>
+        <v>225.4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="3">
-        <f>65.474242+23.570633</f>
-        <v>89.044875000000005</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>16</v>
+      <c r="J3" s="7">
+        <v>88.534999999999997</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>19175.813831250001</v>
+        <v>19955.789000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -701,10 +710,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>1353.2260000000001</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>16</v>
+        <v>998.22799999999995</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -712,10 +721,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>1905.299</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>16</v>
+        <v>1905.81</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -724,7 +733,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>19727.886831250002</v>
+        <v>20863.371000000003</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -743,8 +752,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{060BE0DB-103F-4216-A245-CEE356F7A8FA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -821,6 +833,9 @@
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="K3" s="2">
+        <v>720</v>
+      </c>
       <c r="R3" s="2">
         <v>722</v>
       </c>
@@ -835,6 +850,9 @@
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="K4" s="2">
+        <v>168</v>
+      </c>
       <c r="R4" s="2">
         <v>131</v>
       </c>
@@ -849,22 +867,58 @@
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="C5" s="1">
+        <f t="shared" ref="C5:N5" si="0">+C3+C4</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>888</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1">
-        <f t="shared" ref="Q5" si="0">+Q3+Q4</f>
+        <f t="shared" ref="Q5" si="1">+Q3+Q4</f>
         <v>0</v>
       </c>
       <c r="R5" s="1">
@@ -895,7 +949,9 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="K6" s="11">
+        <v>2483</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -945,11 +1001,15 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3">
+        <v>3174.6770000000001</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>3377.44</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -972,11 +1032,15 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>1787.0640000000001</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1211,11 +1275,15 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>3174.6770000000001</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="6">
+        <v>5164.5039999999999</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -1264,11 +1332,15 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>2009.5909999999999</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>3481.2420000000002</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1314,29 +1386,65 @@
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="C16" s="3">
+        <f t="shared" ref="C16:J16" si="2">+C14-C15</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="2"/>
+        <v>1165.0860000000002</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <f>+K14-K15</f>
+        <v>1683.2619999999997</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" ref="L16:P16" si="3">+L14-L15</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3">
-        <f t="shared" ref="P16" si="1">+P8-P14+P15</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" ref="Q16:R16" si="2">+Q14-Q15</f>
+        <f t="shared" ref="Q16:R16" si="4">+Q14-Q15</f>
         <v>4284.558</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4533.7349999999988</v>
       </c>
       <c r="S16" s="3">
@@ -1379,11 +1487,16 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>785.52800000000002</v>
+      </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <f>1163.928+53.815</f>
+        <v>1217.7430000000002</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1434,11 +1547,15 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>13.442</v>
+      </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <v>14.869</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1484,29 +1601,65 @@
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+      <c r="C19" s="3">
+        <f t="shared" ref="C19:N19" si="5">+C16-C17-C18</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="5"/>
+        <v>366.11600000000021</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="5"/>
+        <v>450.64999999999952</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3">
-        <f t="shared" ref="P19" si="3">+P16-P17+P18</f>
+        <f t="shared" ref="P19" si="6">+P16-P17+P18</f>
         <v>0</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" ref="Q19:R19" si="4">+Q16-Q17-Q18</f>
+        <f t="shared" ref="Q19:R19" si="7">+Q16-Q17-Q18</f>
         <v>1463.019</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1282.3649999999986</v>
       </c>
       <c r="S19" s="3">
@@ -1549,11 +1702,15 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3">
+        <v>12.138</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3">
+        <v>17.541</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -1603,11 +1760,15 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <v>-6.2560000000000002</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>13.166</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -1653,29 +1814,65 @@
       <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="C22" s="3">
+        <f t="shared" ref="C22:N22" si="8">+C19-C20+C21</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="8"/>
+        <v>347.72200000000021</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="8"/>
+        <v>446.27499999999952</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3">
-        <f t="shared" ref="P22:R22" si="5">+P19-P20+P21</f>
+        <f t="shared" ref="P22:R22" si="9">+P19-P20+P21</f>
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1383.748</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1318.1509999999987</v>
       </c>
       <c r="S22" s="3">
@@ -1718,11 +1915,15 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>83.433999999999997</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3">
+        <v>126.453</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -1768,29 +1969,65 @@
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="C24" s="3">
+        <f t="shared" ref="C24:J24" si="10">+C22-C23</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="10"/>
+        <v>264.28800000000024</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <f>+K22-K23</f>
+        <v>319.82199999999955</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" ref="L24:N24" si="11">+L22-L23</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3">
-        <f t="shared" ref="P24:R24" si="6">+P22-P23</f>
+        <f t="shared" ref="P24:R24" si="12">+P22-P23</f>
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1043.1379999999999</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1046.5189999999986</v>
       </c>
       <c r="S24" s="3">
@@ -1872,25 +2109,65 @@
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="C26" s="7" t="e">
+        <f t="shared" ref="C26:J26" si="13">+C24/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D26" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E26" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F26" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="7">
+        <f t="shared" si="13"/>
+        <v>3.3310394373653001</v>
+      </c>
+      <c r="H26" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="7" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J26" s="7" t="e">
-        <f t="shared" ref="J26:R26" si="7">+J24/J27</f>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="K26" s="7">
+        <f>+K24/K27</f>
+        <v>3.6123792850285148</v>
+      </c>
+      <c r="L26" s="7" t="e">
+        <f t="shared" ref="L26:N26" si="14">+L24/L27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J26:R26" si="15">+P24/P27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q26" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>13.430039138943249</v>
       </c>
       <c r="R26" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>12.715596218803899</v>
       </c>
       <c r="S26" s="7">
@@ -1907,11 +2184,15 @@
         <v>3</v>
       </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="G27" s="7">
+        <v>79.340999999999994</v>
+      </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
+      <c r="K27" s="7">
+        <v>88.534999999999997</v>
+      </c>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
